--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -4,136 +4,20 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="测试要点" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="黑盒测试要点" sheetId="1" r:id="rId1"/>
+    <sheet name="灰盒测试要点" sheetId="2" r:id="rId2"/>
+    <sheet name="测试设计" sheetId="3" r:id="rId3"/>
+    <sheet name="查询正交表" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-不确定</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>是否同</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>remove</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-不确定</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A31" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-是否需要关注</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="176">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -206,19 +90,504 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range范围切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash百分比</t>
+  </si>
+  <si>
+    <t>节点配置（新增参数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl alter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find/findOne/count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖非唯一索引、唯一索引、强制唯一索引。</t>
+  </si>
+  <si>
+    <t>dropIndex/dropIdIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listIndex/getIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖普通表/切分表/主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通表改为切分表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引字段覆盖所有的数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update/upsert/findAndUpdate()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、删除索引后，是否真正删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove/findAndRemove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配符、选择符。正序逆序。查询的开头中间结尾。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query:explain/hint/sort/cursor/limit/skip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/size/toArray不考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createIndex/createIdIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、覆盖非唯一索引、唯一索引、强制唯一索引。2、只关注索引相关，如find({索引字段:xxx})3、关注联合索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能+新增参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联合索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>降序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正交因子值1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正交因子值2</t>
+  </si>
+  <si>
+    <t>正交因子值3</t>
+  </si>
+  <si>
+    <t>所有匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单键索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort逆序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort正序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordery升序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordery降序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit</t>
+  </si>
+  <si>
+    <t>explain</t>
+  </si>
+  <si>
+    <t>hint</t>
+  </si>
+  <si>
+    <t>cursor</t>
+  </si>
+  <si>
+    <t>skip</t>
+  </si>
+  <si>
+    <t>索引类型1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引类型2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其余query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景2</t>
+  </si>
+  <si>
+    <t>场景3</t>
+  </si>
+  <si>
+    <t>场景4</t>
+  </si>
+  <si>
+    <t>场景5</t>
+  </si>
+  <si>
+    <t>场景6</t>
+  </si>
+  <si>
+    <t>场景7</t>
+  </si>
+  <si>
+    <t>正交结果如下：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一索引，插入记录</t>
+  </si>
+  <si>
+    <t>存在唯一索引，插入不合法的记录：索引值已存在</t>
+  </si>
+  <si>
+    <t>存在强制唯一索引，插入不合法的记录：索引值已存在、存在两条不指定索引值的记录</t>
+  </si>
+  <si>
+    <t>插入记录，指定合法的_id值</t>
+  </si>
+  <si>
+    <t>插入记录，指定_id值已存在</t>
+  </si>
+  <si>
+    <t>在主子，插入指定子表分区键值的记录</t>
+  </si>
+  <si>
+    <t>存在强制唯一索引，索引为多字段，插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一索引，更新记录的索引值已存在</t>
+  </si>
+  <si>
+    <t>存在强制唯一索引，更新记录的索引值已存在、更新了两条记录（索引字段都不存在）</t>
+  </si>
+  <si>
+    <t>主子表上，更新记录的子/主表分区键值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新_id值为已存在的值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新_id值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，插入记录，覆盖所有数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在多字段的唯一索引，upsert记录，覆盖部分更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在强制唯一索引，findAndUpdate记录，覆盖部分更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分表上，存在唯一索引，执行truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表上，存在强制唯一索引，执行truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通表上，存在非唯一索引，执行truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，update索引值为其他数据类型，覆盖部分更新符，覆盖所有数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       因子值
+因子    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在多字段的非唯一索引，remove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一索引，findAndRemove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在强制唯一索引，remove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort逆序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询（思路见查询正交表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:-1})，执行explain，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:1})，执行explain，执行find().hint()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordery升序降序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行find().sort({索引字段:1})，执行explain，使用cursor，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:1})，执行explain，执行find().limit()，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:-1})，执行explain，执行find().limit()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行findOne().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在强制唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行count().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，检查索引是否可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，kill-9节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复创建索引；索引字段相同；索引名相同</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id索引已存在时，创建Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引不存在时，删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id索引不存在时，删除Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据管理（基本功能+新增参数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>cs创建(options新增参数)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range切分</t>
+    <t>cs创建时，新增参数IndexEngineType的参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs创建</t>
+  </si>
+  <si>
+    <t>普通集合alter为切分表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分（关注基本功能）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -226,34 +595,108 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hash百分比</t>
+    <t>hash百分比切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步（关注基本功能）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引（基本功能+可靠性异常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引时，正常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引时，正常重启备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引时，异常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引时，异常重启备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引时，全网掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=-1时新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=0时新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=3时新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=2时新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>节点配置（新增参数）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>……</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各种聚集符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cl alter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>导入导出工具</t>
+    <t>rocksdbwritebuff参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbmaxwritebuffernumber参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbblockcachesize参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbnumthread参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbconfigstr参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上参数都取默认值，查看是否生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbconfigstr配置一个参数，查看是否生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>优先级低，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否测试</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -261,114 +704,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update/upsert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>相互覆盖即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>相互覆盖即可。匹配符选取几个测试，不作为重点。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>find/findOne/count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query:explain/hint/sort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor/limit/size/skip/toArray不考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>findAndRemove()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>findAndUpdate()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖非唯一索引、唯一索引、强制唯一索引。</t>
-  </si>
-  <si>
-    <t>createIndex/createIndexOffline/createIdIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropIndex/dropIdIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listIndex/getIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖普通表/切分表/主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通表改为切分表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引字段覆盖所有的数据类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不确定是否有影响</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分区键多字段，分区键为不同数据类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挂载子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分离子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、覆盖非唯一索引、唯一索引、强制唯一索引。2、覆盖普通表/切分表/主子表。3、只关注索引相关，如find({索引字段:xxx})</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增节点</t>
+    <t>是否测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注：没有关注数据类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -376,7 +716,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,25 +732,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -433,7 +760,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -456,16 +783,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -828,11 +1209,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2"/>
-    <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.125" style="2" customWidth="1"/>
     <col min="3" max="16384" width="12.5" style="2"/>
   </cols>
   <sheetData>
@@ -844,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
@@ -852,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
@@ -860,10 +1241,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
@@ -871,10 +1252,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -882,7 +1263,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
@@ -895,75 +1276,72 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" customHeight="1">
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
-      <c r="B9" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1">
-      <c r="B10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>45</v>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
+      <c r="A13" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="16" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
@@ -976,15 +1354,15 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1">
@@ -994,127 +1372,111 @@
     </row>
     <row r="23" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" customHeight="1">
+      <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15" customHeight="1">
-      <c r="A36" s="2" t="s">
+    <row r="33" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" customHeight="1">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" customHeight="1">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15" customHeight="1">
-      <c r="A47" s="2" t="s">
+    <row r="38" spans="1:2" ht="15" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1122,10 +1484,679 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="61.25" style="11" customWidth="1"/>
+    <col min="2" max="2" width="59.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="14" customFormat="1">
+      <c r="A1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="5" customFormat="1">
+      <c r="A2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="5" customFormat="1">
+      <c r="A9" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="5" customFormat="1">
+      <c r="A16" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" s="5" customFormat="1">
+      <c r="A25" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" s="5" customFormat="1">
+      <c r="A34" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" s="5" customFormat="1">
+      <c r="A48" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" s="5" customFormat="1">
+      <c r="A56" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" s="5" customFormat="1">
+      <c r="A60" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" s="5" customFormat="1">
+      <c r="A66" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" s="17" customFormat="1">
+      <c r="A75" s="16"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:I20"/>
+  <sheetFormatPr defaultColWidth="13.875" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="2" spans="2:9" ht="25.5" customHeight="1">
+      <c r="B2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="17.25" customHeight="1">
+      <c r="B3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="19.5" customHeight="1">
+      <c r="B4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="2:9" ht="17.25" customHeight="1">
+      <c r="B5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="2:9" ht="18" customHeight="1">
+      <c r="B7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="2:9" ht="18" customHeight="1">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="G18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -16,8 +16,79 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A44" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这部分未写设计</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>yuting:</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>待补充</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="191">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -391,12 +462,6 @@
     <t>插入记录，指定合法的_id值</t>
   </si>
   <si>
-    <t>插入记录，指定_id值已存在</t>
-  </si>
-  <si>
-    <t>在主子，插入指定子表分区键值的记录</t>
-  </si>
-  <si>
     <t>存在强制唯一索引，索引为多字段，插入记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -419,14 +484,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在非唯一索引，插入记录，覆盖所有数据类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在多字段的唯一索引，upsert记录，覆盖部分更新符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>存在强制唯一索引，findAndUpdate记录，覆盖部分更新符</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -444,10 +501,6 @@
   </si>
   <si>
     <t>普通表上，存在非唯一索引，执行truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在非唯一索引，update索引值为其他数据类型，覆盖部分更新符，覆盖所有数据类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -456,6 +509,185 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>存在强制唯一索引，remove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort逆序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>explain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询（思路见查询正交表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:-1})，执行explain，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:1})，执行explain，执行find().hint()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordery升序降序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行find().sort({索引字段:1})，执行explain，使用cursor，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:1})，执行explain，执行find().limit()，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:-1})，执行explain，执行find().limit()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行findOne().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分选择符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在强制唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行count().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，kill-9节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复创建索引；索引字段相同；索引名相同</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id索引已存在时，创建Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引不存在时，删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id索引不存在时，删除Id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据管理（基本功能+新增参数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs创建(options新增参数)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs创建</t>
+  </si>
+  <si>
+    <t>普通集合alter为切分表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步（关注基本功能）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引（基本功能+可靠性异常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=-1时新增节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点配置（新增参数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbwritebuff参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbmaxwritebuffernumber参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbblockcachesize参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbnumthread参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbconfigstr参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上参数都取默认值，查看是否生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注：没有关注数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，插入记录，覆盖所有数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主子表上，插入指定子表分区键值的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录，指定_id值已存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，update索引值为其他数据类型，覆盖部分更新符，覆盖所有数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在多字段的唯一索引，upsert记录，覆盖部分更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>存在多字段的非唯一索引，remove记录时的删除条件为索引字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -464,63 +696,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在强制唯一索引，remove记录时的删除条件为索引字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分选择符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sort逆序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分匹配符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>explain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询（思路见查询正交表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:-1})，执行explain，覆盖部分匹配符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在非唯一单键索引，ordery为升序，执行find().sort({索引字段:1})，执行explain，执行find().hint()，覆盖部分选择符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ordery升序降序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在非唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行find().sort({索引字段:1})，执行explain，使用cursor，覆盖部分匹配符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:1})，执行explain，执行find().limit()，覆盖部分匹配符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:-1})，执行explain，执行find().limit()，覆盖部分选择符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行findOne().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分选择符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在强制唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行count().sort({索引字段:-1})，执行explain，执行find().skip()，覆盖部分匹配符</t>
+    <t>cs创建时，新增参数IndexEngineType的参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分（关注基本功能）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbconfigstr配置一个参数，查看是否生效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -528,187 +712,120 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建Id索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除Id索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>get索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，kill-9节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复创建索引；索引字段相同；索引名相同</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id索引已存在时，创建Id索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引不存在时，删除索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id索引不存在时，删除Id索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据管理（基本功能+新增参数）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs创建(options新增参数)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs创建时，新增参数IndexEngineType的参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs创建</t>
-  </si>
-  <si>
-    <t>普通集合alter为切分表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>切分（关注基本功能）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range范围切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash百分比切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据同步（关注基本功能）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引（基本功能+可靠性异常）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引时，正常重启主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引时，正常重启备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引时，异常重启主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引时，异常重启备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引时，全网掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w=-1时新增节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w=0时新增节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w=3时新增节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w=2时新增节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点配置（新增参数）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbwritebuff参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbmaxwritebuffernumber参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbblockcachesize参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbnumthread参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbconfigstr参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以上参数都取默认值，查看是否生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbconfigstr配置一个参数，查看是否生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>$group</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>优先级低，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否测试</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注：没有关注数据类型</t>
+    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，已存在数据，正常重启节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证$group的功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新旧索引是否能并存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼容性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持x86和power机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要验x86，power验基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反复创建删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，正常重启备节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，异常重启主节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，异常重启备节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，正常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发创建多个索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，主节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，备节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，全网掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range范围切分，分区键为单个字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash百分比切分，分区键为多个字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cs1指定为旧的引擎，创建索引1，创建cs2指定为新引擎，创建索引2，验证索引1、2是否可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$match和$first执行聚集查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行创建索引、增删改查操作后，执行事务回滚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行创建索引、增删改查操作后，执行事务提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行sql create index创建索引，执行增删改查验证索引可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集（简单验证功能可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务（简单验证功能可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql（简单验证功能可用）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -716,7 +833,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -734,6 +851,42 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -844,9 +997,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1209,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2"/>
@@ -1341,7 +1494,7 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
@@ -1404,7 +1557,7 @@
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
@@ -1422,13 +1575,11 @@
         <v>25</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>171</v>
-      </c>
+      <c r="A34" s="4"/>
     </row>
     <row r="35" spans="1:2" ht="15" customHeight="1">
       <c r="A35" s="4"/>
@@ -1438,7 +1589,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" customHeight="1">
@@ -1453,22 +1604,41 @@
     </row>
     <row r="40" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>174</v>
+        <v>148</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A42" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4"/>
+  <dimension ref="A4:A5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="4" spans="1:1">
@@ -1476,18 +1646,20 @@
         <v>40</v>
       </c>
     </row>
+    <row r="5" spans="1:1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="61.25" style="11" customWidth="1"/>
+    <col min="1" max="1" width="72.375" style="11" customWidth="1"/>
     <col min="2" max="2" width="59.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1506,7 +1678,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1519,7 +1691,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
         <v>96</v>
@@ -1530,12 +1702,12 @@
         <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="5" customFormat="1">
@@ -1545,36 +1717,36 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="11" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="5" customFormat="1">
@@ -1584,272 +1756,342 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="11" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="11" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="5" customFormat="1">
       <c r="A25" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="5" customFormat="1">
       <c r="A34" s="12" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="11" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B37" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="11" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>136</v>
+        <v>125</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="11" t="s">
-        <v>137</v>
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="11" t="s">
-        <v>138</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="B41" s="15"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="11" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="11" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="11" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" s="5" customFormat="1">
-      <c r="A48" s="12" t="s">
-        <v>143</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="11" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="11" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="11" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="11" t="s">
-        <v>15</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="11" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="11" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" s="5" customFormat="1">
-      <c r="A56" s="12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="11" t="s">
-        <v>149</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="16"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="16"/>
+    </row>
+    <row r="57" spans="1:1" s="5" customFormat="1">
+      <c r="A57" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" s="5" customFormat="1">
-      <c r="A60" s="12" t="s">
-        <v>151</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="11" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="11" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" s="5" customFormat="1">
-      <c r="A66" s="12" t="s">
-        <v>163</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" s="5" customFormat="1">
+      <c r="A65" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="11" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="11" t="s">
-        <v>166</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" s="5" customFormat="1">
+      <c r="A69" s="12" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="11" t="s">
-        <v>169</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" s="5" customFormat="1">
+      <c r="A72" s="12" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" s="17" customFormat="1">
-      <c r="A75" s="16"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" s="5" customFormat="1">
+      <c r="A81" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" s="5" customFormat="1">
+      <c r="A84" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" s="5" customFormat="1">
+      <c r="A88" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" s="5" customFormat="1">
+      <c r="A91" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="11" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1860,7 +2102,7 @@
   <sheetData>
     <row r="2" spans="2:9" ht="25.5" customHeight="1">
       <c r="B2" s="10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>67</v>
@@ -1947,7 +2189,7 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>82</v>
@@ -1982,19 +2224,19 @@
         <v>72</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>75</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -2004,7 +2246,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>74</v>
@@ -2036,7 +2278,7 @@
         <v>74</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>78</v>
@@ -2078,7 +2320,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>73</v>
@@ -2104,13 +2346,13 @@
         <v>59</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>73</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>78</v>
@@ -2136,7 +2378,7 @@
         <v>73</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>78</v>
@@ -2151,7 +2393,7 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="4" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="196">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -377,14 +377,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sort逆序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sort正序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ordery升序</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,9 +394,6 @@
     <t>hint</t>
   </si>
   <si>
-    <t>cursor</t>
-  </si>
-  <si>
     <t>skip</t>
   </si>
   <si>
@@ -484,19 +473,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在强制唯一索引，findAndUpdate记录，覆盖部分更新符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>切分表上，存在唯一索引，执行truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主子表上，存在强制唯一索引，执行truncate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -517,10 +494,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sort逆序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>explain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -545,10 +518,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在非唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行find().sort({索引字段:1})，执行explain，使用cursor，覆盖部分匹配符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>存在唯一单键索引，ordery为降序，执行find().sort({索引字段:1})，执行explain，执行find().limit()，覆盖部分匹配符</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -680,7 +649,152 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在非唯一索引，update索引值为其他数据类型，覆盖部分更新符，覆盖所有数据类型</t>
+    <t>存在多字段的非唯一索引，remove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在唯一索引，findAndRemove记录时的删除条件为索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs创建时，新增参数IndexEngineType的参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分（关注基本功能）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocksdbconfigstr配置一个参数，查看是否生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，检查索引是否可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证$group的功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只需简单验证功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新旧索引是否能并存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼容性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持x86和power机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要验x86，power验基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反复创建删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，正常重启备节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，异常重启主节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，异常重启备节点</t>
+  </si>
+  <si>
+    <t>创建索引过程中，正常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，主节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，备节点磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发创建多个索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，主节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，备节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建索引过程中，全网掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range范围切分，分区键为单个字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash百分比切分，分区键为多个字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cs1指定为旧的引擎，创建索引1，创建cs2指定为新引擎，创建索引2，验证索引1、2是否可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$match和$first执行聚集查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行创建索引、增删改查操作后，执行事务回滚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行创建索引、增删改查操作后，执行事务提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行sql create index创建索引，执行增删改查验证索引可用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集（简单验证功能可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务（简单验证功能可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql（简单验证功能可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，update索引值为其他数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在多字段的唯一索引，upsert记录，覆盖所有数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，update记录，覆盖部分更新符</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -688,144 +802,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在多字段的非唯一索引，remove记录时的删除条件为索引字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在唯一索引，findAndRemove记录时的删除条件为索引字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs创建时，新增参数IndexEngineType的参数校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>切分（关注基本功能）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rocksdbconfigstr配置一个参数，查看是否生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，检查索引是否可用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，已存在数据，正常重启节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只需简单验证$group的功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只需简单验证功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只需简单验证功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新旧索引是否能并存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兼容性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>支持x86和power机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主要验x86，power验基本功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反复创建删除索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，正常重启备节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，异常重启主节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，异常重启备节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，正常重启主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，备节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发创建多个索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，主节点主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，备节点主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，全网掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range范围切分，分区键为单个字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash百分比切分，分区键为多个字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建cs1指定为旧的引擎，创建索引1，创建cs2指定为新引擎，创建索引2，验证索引1、2是否可用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$match和$first执行聚集查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行创建索引、增删改查操作后，执行事务回滚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行创建索引、增删改查操作后，执行事务提交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行sql create index创建索引，执行增删改查验证索引可用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集（简单验证功能可用）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务（简单验证功能可用）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql（简单验证功能可用）</t>
+    <t>存在强制唯一索引，findAndUpdate记录，覆盖部分更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在非唯一索引，update索引值为已存在的值，update多条记录使其索引字段不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一个集合中创建多个索引，执行增删改查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在索引时，remove不存在的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表上，存在唯一索引、强制唯一索引，执行truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit(0)、limit(超过记录数)、skip(0)、skip(超过记录数)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort升序</t>
+  </si>
+  <si>
+    <t>sort降序</t>
+  </si>
+  <si>
+    <t>存在非唯一联合索引，有些索引字段的ordery为升序，有些索引字段的ordery为降序，执行find().sort({索引字段:1})，执行explain，覆盖部分匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，已存在数据，正常重启主节点、数据组所有节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（写缓存大小*个数）小于（实际物理内存+虚拟内存）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -979,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1000,6 +1019,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1494,7 +1516,7 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
@@ -1557,7 +1579,7 @@
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
@@ -1575,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" customHeight="1">
@@ -1589,7 +1611,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" customHeight="1">
@@ -1604,28 +1626,28 @@
     </row>
     <row r="40" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="17" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1656,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="72.375" style="11" customWidth="1"/>
@@ -1678,36 +1700,36 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="5" customFormat="1">
@@ -1717,375 +1739,410 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="11" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="5" customFormat="1">
+      <c r="A19" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="19" customFormat="1">
+      <c r="A20" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="B14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" s="5" customFormat="1">
-      <c r="A16" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="5" customFormat="1">
+      <c r="A28" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" s="5" customFormat="1">
-      <c r="A25" s="12" t="s">
+    <row r="31" spans="1:2">
+      <c r="A31" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="11" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" s="5" customFormat="1">
-      <c r="A34" s="12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B35" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" s="5" customFormat="1">
+      <c r="A39" s="12" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="11" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" s="15"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="11" t="s">
-        <v>127</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="11" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="11" t="s">
-        <v>161</v>
+        <v>116</v>
+      </c>
+      <c r="B44" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="11" t="s">
-        <v>128</v>
+        <v>117</v>
+      </c>
+      <c r="B45" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="11" t="s">
-        <v>174</v>
+        <v>118</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="11" t="s">
-        <v>171</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B47" s="15"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="11" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="11" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="11" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="11" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="11" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="11" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="16"/>
+      <c r="A55" s="11" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="16"/>
-    </row>
-    <row r="57" spans="1:1" s="5" customFormat="1">
-      <c r="A57" s="12" t="s">
-        <v>133</v>
+      <c r="A56" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="11" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="11" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="11" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="11" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="11" t="s">
-        <v>16</v>
-      </c>
+      <c r="A61" s="16"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" s="5" customFormat="1">
-      <c r="A65" s="12" t="s">
-        <v>158</v>
+      <c r="A62" s="16"/>
+    </row>
+    <row r="63" spans="1:1" s="5" customFormat="1">
+      <c r="A63" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="11" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" s="5" customFormat="1">
-      <c r="A69" s="12" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" s="5" customFormat="1">
-      <c r="A72" s="12" t="s">
-        <v>141</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" s="5" customFormat="1">
+      <c r="A71" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="11" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="11" t="s">
-        <v>144</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" s="5" customFormat="1">
+      <c r="A75" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="11" t="s">
-        <v>147</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" s="5" customFormat="1">
+      <c r="A78" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" s="5" customFormat="1">
-      <c r="A81" s="12" t="s">
-        <v>188</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="11" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" s="5" customFormat="1">
-      <c r="A84" s="12" t="s">
-        <v>189</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="11" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="11" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="11" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:1" s="5" customFormat="1">
       <c r="A88" s="12" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="11" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:1" s="5" customFormat="1">
       <c r="A91" s="12" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="11" t="s">
-        <v>183</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" s="5" customFormat="1">
+      <c r="A95" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" s="5" customFormat="1">
+      <c r="A98" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="11" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2159,7 @@
   <sheetData>
     <row r="2" spans="2:9" ht="25.5" customHeight="1">
       <c r="B2" s="10" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>67</v>
@@ -2116,7 +2173,7 @@
     </row>
     <row r="3" spans="2:9" ht="17.25" customHeight="1">
       <c r="B3" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>45</v>
@@ -2130,7 +2187,7 @@
     </row>
     <row r="4" spans="2:9" ht="19.5" customHeight="1">
       <c r="B4" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>72</v>
@@ -2184,18 +2241,18 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>63</v>
@@ -2207,15 +2264,15 @@
         <v>60</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>45</v>
@@ -2224,46 +2281,46 @@
         <v>72</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>45</v>
@@ -2272,72 +2329,68 @@
         <v>59</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="2:9" s="19" customFormat="1">
+      <c r="B14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="I14" s="20"/>
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="I15" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -2346,24 +2399,24 @@
         <v>59</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="H16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -2372,19 +2425,19 @@
         <v>59</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -2393,7 +2446,7 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7845" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="黑盒测试要点" sheetId="1" r:id="rId1"/>
     <sheet name="灰盒测试要点" sheetId="2" r:id="rId2"/>
     <sheet name="测试设计" sheetId="3" r:id="rId3"/>
     <sheet name="查询正交表" sheetId="6" r:id="rId4"/>
+    <sheet name="匹配符测试要点" sheetId="7" r:id="rId5"/>
+    <sheet name="元字符测试要点" sheetId="8" r:id="rId6"/>
+    <sheet name="自动化脚本" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -88,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="329">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -845,6 +848,522 @@
   </si>
   <si>
     <t>（写缓存大小*个数）小于（实际物理内存+虚拟内存）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配符</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作的记录类型</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试要点</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$gt</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有数据类型</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$gte</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lt</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$lte</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$et</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$ne</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$isnull</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$exists</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$type</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$in</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组、其他也生效</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为数组（关注所有数据类型）、记录为非数组（关注所有数据类型）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$nin</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$size</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组，其他不生效</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为数组（关注所有数据类型）、记录为非数组</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$all</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$+标识符</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数组</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为数组（关注所有数据类型）</t>
+  </si>
+  <si>
+    <t>$elemMatch</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为对象（关注所有数据类型）、多层嵌套</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$mod</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为数值型（整型、长整型、浮点型）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$regex</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录为字符串（覆盖所有元字符）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$and</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑与</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$or</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑非</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$not</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑或</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>^</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配以……开头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配任意字符（除了换行）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配以……结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>|</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交替</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grouping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把一类字符括起来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配0次或者更多次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配1次或者更多次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配0次或者1次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{n}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配n次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配n+次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{n,}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{n,m}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配n-m次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\t</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>newline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\r</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>return</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\cK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>control char</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\x{},\x00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>十六进制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alarm bell，系统响铃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>form feed，换页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\o{},\000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>八进制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[a-z]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1-9]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配非字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配字符（字母数字和_）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配空格whitespace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配非空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配十进制数字字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配非数字字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配单词边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配非单词边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>横向制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非横向制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纵向制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非纵向制表符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只匹配字符串开头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\Z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只匹配字符串结尾、换行之前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只匹配字符串结尾</t>
+  </si>
+  <si>
+    <t>\z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matcher_1.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matcher_2.js</t>
+  </si>
+  <si>
+    <t>matcher_3.js</t>
+  </si>
+  <si>
+    <t>matcher_4.js</t>
+  </si>
+  <si>
+    <t>matcher_5.js</t>
+  </si>
+  <si>
+    <t>matcher_6.js</t>
+  </si>
+  <si>
+    <t>matcher_1_combined.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matcher_2_combined.js</t>
+  </si>
+  <si>
+    <t>matcher_3_combined.js</t>
+  </si>
+  <si>
+    <t>$gt/$gte/$lt/$lte/$et/$ne</t>
+  </si>
+  <si>
+    <t>$gt/$gte/$lt/$lte/$et/$ne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$isnull/$exists/$type</t>
+  </si>
+  <si>
+    <t>$in/$nin/$all/$identifier</t>
+  </si>
+  <si>
+    <t>$elemMatch</t>
+  </si>
+  <si>
+    <t>$mod</t>
+  </si>
+  <si>
+    <t>$regex</t>
+  </si>
+  <si>
+    <t>$in/$nin/$all/$elemMatch/$mod/$regex</t>
+  </si>
+  <si>
+    <t>多键索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -852,7 +1371,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -911,6 +1430,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -932,7 +1457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -994,11 +1519,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1022,6 +1619,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2454,4 +3057,702 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="C5:F26"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="5" max="5" width="62.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:6">
+      <c r="C5" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="3:6">
+      <c r="C6" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="3:6">
+      <c r="C11" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="3:6">
+      <c r="C12" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="3:6">
+      <c r="C13" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="3:6">
+      <c r="C14" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="3:6">
+      <c r="C15" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="3:6">
+      <c r="C16" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="C18" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="C19" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="C20" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="C21" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="C7:D49"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="7" spans="3:4">
+      <c r="C7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4">
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4">
+      <c r="C9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4">
+      <c r="C10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4">
+      <c r="C11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4">
+      <c r="C12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4">
+      <c r="C13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4">
+      <c r="C15" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4">
+      <c r="C16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18" t="s">
+        <v>255</v>
+      </c>
+      <c r="D18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4">
+      <c r="C20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" t="s">
+        <v>263</v>
+      </c>
+      <c r="D23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" t="s">
+        <v>268</v>
+      </c>
+      <c r="D26" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" t="s">
+        <v>271</v>
+      </c>
+      <c r="D28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" t="s">
+        <v>273</v>
+      </c>
+      <c r="D29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" t="s">
+        <v>277</v>
+      </c>
+      <c r="D30" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" t="s">
+        <v>281</v>
+      </c>
+      <c r="D34" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" t="s">
+        <v>285</v>
+      </c>
+      <c r="D36" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D37" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" t="s">
+        <v>289</v>
+      </c>
+      <c r="D38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" t="s">
+        <v>291</v>
+      </c>
+      <c r="D39" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40" t="s">
+        <v>297</v>
+      </c>
+      <c r="D40" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" t="s">
+        <v>299</v>
+      </c>
+      <c r="D41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4">
+      <c r="C42" t="s">
+        <v>301</v>
+      </c>
+      <c r="D42" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4">
+      <c r="C43" t="s">
+        <v>302</v>
+      </c>
+      <c r="D43" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4">
+      <c r="C45" t="s">
+        <v>293</v>
+      </c>
+      <c r="D45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4">
+      <c r="C46" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4">
+      <c r="C47" t="s">
+        <v>305</v>
+      </c>
+      <c r="D47" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4">
+      <c r="C48" t="s">
+        <v>307</v>
+      </c>
+      <c r="D48" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4">
+      <c r="C49" t="s">
+        <v>310</v>
+      </c>
+      <c r="D49" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B12:G20"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="2:7">
+      <c r="B12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" t="s">
+        <v>323</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15" t="s">
+        <v>324</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C17" t="s">
+        <v>326</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" t="s">
+        <v>327</v>
+      </c>
+      <c r="G20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="332">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1364,6 +1364,18 @@
   </si>
   <si>
     <t>多键索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试的匹配符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1595,7 +1607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1625,6 +1637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3070,13 +3083,13 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:6">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="27" t="s">
         <v>198</v>
       </c>
       <c r="F5" s="2"/>
@@ -3645,108 +3658,120 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B12:G20"/>
+  <dimension ref="B11:D20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="3" max="3" width="40.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="2:7">
-      <c r="B12" t="s">
+    <row r="11" spans="2:4">
+      <c r="B11" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="G12" t="s">
+      <c r="D12" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" t="s">
+    <row r="13" spans="2:4">
+      <c r="B13" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G13" t="s">
+      <c r="D13" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" t="s">
+    <row r="14" spans="2:4">
+      <c r="B14" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G14" t="s">
+      <c r="D14" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" t="s">
+    <row r="15" spans="2:4">
+      <c r="B15" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G15" t="s">
+      <c r="D15" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" t="s">
+    <row r="16" spans="2:4">
+      <c r="B16" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="G16" t="s">
+      <c r="D16" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" t="s">
+    <row r="17" spans="2:4">
+      <c r="B17" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G17" t="s">
+      <c r="D17" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" t="s">
+    <row r="18" spans="2:4">
+      <c r="B18" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G18" t="s">
+      <c r="D18" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" t="s">
+    <row r="19" spans="2:4">
+      <c r="B19" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G19" t="s">
+      <c r="D19" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" t="s">
+    <row r="20" spans="2:4">
+      <c r="B20" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="G20" t="s">
+      <c r="D20" s="6" t="s">
         <v>328</v>
       </c>
     </row>

--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7845" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7845" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="黑盒测试要点" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,9 @@
     <sheet name="测试设计" sheetId="3" r:id="rId3"/>
     <sheet name="查询正交表" sheetId="6" r:id="rId4"/>
     <sheet name="匹配符测试要点" sheetId="7" r:id="rId5"/>
-    <sheet name="元字符测试要点" sheetId="8" r:id="rId6"/>
-    <sheet name="自动化脚本" sheetId="9" r:id="rId7"/>
+    <sheet name="自动化脚本" sheetId="9" r:id="rId6"/>
+    <sheet name="limit skip" sheetId="10" r:id="rId7"/>
+    <sheet name="可靠性测试" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -55,43 +56,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>yuting:</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>待补充</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="298">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -852,461 +818,162 @@
   </si>
   <si>
     <t>匹配符</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>操作的记录类型</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>测试要点</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$gt</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>所有</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>所有数据类型</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$gte</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$lt</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$lte</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$et</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$ne</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$isnull</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$exists</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$type</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$in</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>数组、其他也生效</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为数组（关注所有数据类型）、记录为非数组（关注所有数据类型）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$nin</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$size</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>数组，其他不生效</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为数组（关注所有数据类型）、记录为非数组</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$all</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$+标识符</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>数组</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为数组（关注所有数据类型）</t>
   </si>
   <si>
     <t>$elemMatch</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>对象</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为对象（关注所有数据类型）、多层嵌套</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$mod</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>数值</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为数值型（整型、长整型、浮点型）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$regex</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>字符串</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>记录为字符串（覆盖所有元字符）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$and</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>逻辑与</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$or</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>逻辑非</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>$not</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>逻辑或</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>\</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>^</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配以……开头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配任意字符（除了换行）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>$</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配以……结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>|</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交替</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Grouping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>把一类字符括起来</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配0次或者更多次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配1次或者更多次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配0次或者1次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{n}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配n次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配n+次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{n,}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{n,m}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配n-m次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\n</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>newline</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\r</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>return</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\e</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\cK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>control char</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\x{},\x00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>十六进制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alarm bell，系统响铃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>form feed，换页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\o{},\000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>八进制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[a-z]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1-9]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\w</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\W</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配非字符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配字符（字母数字和_）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配空格whitespace</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配非空格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配十进制数字字符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配非数字字符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配单词边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配非单词边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>横向制表符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非横向制表符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\h</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纵向制表符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非纵向制表符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只匹配字符串开头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\Z</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只匹配字符串结尾、换行之前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只匹配字符串结尾</t>
-  </si>
-  <si>
-    <t>\z</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>matcher_1.js</t>
@@ -1348,9 +1015,6 @@
     <t>$isnull/$exists/$type</t>
   </si>
   <si>
-    <t>$in/$nin/$all/$identifier</t>
-  </si>
-  <si>
     <t>$elemMatch</t>
   </si>
   <si>
@@ -1360,9 +1024,6 @@
     <t>$regex</t>
   </si>
   <si>
-    <t>$in/$nin/$all/$elemMatch/$mod/$regex</t>
-  </si>
-  <si>
     <t>多键索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1376,6 +1037,178 @@
   </si>
   <si>
     <t>索引类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$in/$nin/$size/$all/$identifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$in/$nin/$size/$all/$elemMatch/$mod/$regex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit(0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit(N)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit(N+1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skip(0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skip(N)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skip(N+1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit(n),n取1到N-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skip(n),n取1到N-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lte_lt_match()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试脚本名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>函数名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_isnull_match()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matcher_2_combined.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_exists_match()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gt_ne_match()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>概述：limit和skip的测试点覆盖在联合索引的查询脚本下（matcher_*_combined.js）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>假定：cl.find()返回N条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试无法验证，不做测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发执行增删改查，使用同一个索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发执行增删改查，使用不同索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发创建/删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常重启备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常重启主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常重启备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点主机异常掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点主机异常掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全网掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在索引，并发执行增删改查时，发生异常：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除索引过程中，发生异常：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在数据和索引，无操作时，发生异常：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旧引擎中有bug,在新引擎中暂时不验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全网掉电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1405,13 +1238,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1448,6 +1274,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1469,7 +1302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1603,11 +1436,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1625,9 +1487,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1638,6 +1500,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2276,19 +2156,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:A5"/>
+  <dimension ref="A4:D4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:1"/>
+      <c r="D4" t="s">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2916,8 +2797,12 @@
       <c r="B12" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="E12" s="6" t="s">
         <v>105</v>
       </c>
@@ -2956,7 +2841,9 @@
       <c r="H13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="14" spans="2:9" s="19" customFormat="1">
       <c r="B14" s="8" t="s">
@@ -2980,14 +2867,20 @@
       <c r="H14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="20"/>
+      <c r="I14" s="6" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="C15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>72</v>
+      </c>
       <c r="E15" s="6" t="s">
         <v>105</v>
       </c>
@@ -3343,310 +3236,121 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C7:D49"/>
+  <dimension ref="B11:D20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="3" max="3" width="43.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="7" spans="3:4">
-      <c r="C7" t="s">
+    <row r="11" spans="2:4">
+      <c r="B11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="6" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="8" spans="3:4">
-      <c r="C8" t="s">
+      <c r="C12" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C13" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="6" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="9" spans="3:4">
-      <c r="C9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C15" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="6" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="10" spans="3:4">
-      <c r="C10" t="s">
+      <c r="C16" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C17" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="6" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="11" spans="3:4">
-      <c r="C11" t="s">
+      <c r="C18" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C19" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="6" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="12" spans="3:4">
-      <c r="C12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D12" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4">
-      <c r="C13" t="s">
-        <v>246</v>
-      </c>
-      <c r="D13" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="15" spans="3:4">
-      <c r="C15" t="s">
-        <v>249</v>
-      </c>
-      <c r="D15" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="3:4">
-      <c r="C16" t="s">
+      <c r="C20" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="D16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4">
-      <c r="C17" t="s">
-        <v>253</v>
-      </c>
-      <c r="D17" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4">
-      <c r="C18" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4">
-      <c r="C19" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4">
-      <c r="C20" t="s">
-        <v>259</v>
-      </c>
-      <c r="D20" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4">
-      <c r="C22" t="s">
-        <v>261</v>
-      </c>
-      <c r="D22" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4">
-      <c r="C23" t="s">
-        <v>263</v>
-      </c>
-      <c r="D23" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4">
-      <c r="C24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4">
-      <c r="C25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4">
-      <c r="C26" t="s">
-        <v>268</v>
-      </c>
-      <c r="D26" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4">
-      <c r="C27" t="s">
-        <v>269</v>
-      </c>
-      <c r="D27" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4">
-      <c r="C28" t="s">
-        <v>271</v>
-      </c>
-      <c r="D28" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4">
-      <c r="C29" t="s">
-        <v>273</v>
-      </c>
-      <c r="D29" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4">
-      <c r="C30" t="s">
-        <v>277</v>
-      </c>
-      <c r="D30" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4">
-      <c r="C34" t="s">
-        <v>281</v>
-      </c>
-      <c r="D34" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4">
-      <c r="C35" t="s">
-        <v>282</v>
-      </c>
-      <c r="D35" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4">
-      <c r="C36" t="s">
-        <v>285</v>
-      </c>
-      <c r="D36" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4">
-      <c r="C37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D37" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4">
-      <c r="C38" t="s">
-        <v>289</v>
-      </c>
-      <c r="D38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4">
-      <c r="C39" t="s">
-        <v>291</v>
-      </c>
-      <c r="D39" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4">
-      <c r="C40" t="s">
-        <v>297</v>
-      </c>
-      <c r="D40" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4">
-      <c r="C41" t="s">
-        <v>299</v>
-      </c>
-      <c r="D41" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4">
-      <c r="C42" t="s">
-        <v>301</v>
-      </c>
-      <c r="D42" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4">
-      <c r="C43" t="s">
-        <v>302</v>
-      </c>
-      <c r="D43" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4">
-      <c r="C45" t="s">
-        <v>293</v>
-      </c>
-      <c r="D45" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4">
-      <c r="C46" t="s">
-        <v>295</v>
-      </c>
-      <c r="D46" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4">
-      <c r="C47" t="s">
-        <v>305</v>
-      </c>
-      <c r="D47" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4">
-      <c r="C48" t="s">
-        <v>307</v>
-      </c>
-      <c r="D48" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4">
-      <c r="C49" t="s">
-        <v>310</v>
-      </c>
-      <c r="D49" t="s">
-        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3658,126 +3362,318 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B11:D20"/>
+  <dimension ref="C2:F13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="21.125" customWidth="1"/>
+    <col min="4" max="4" width="23.375" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="2:4">
-      <c r="B11" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>328</v>
-      </c>
+    <row r="2" spans="3:6">
+      <c r="C2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6">
+      <c r="C3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6">
+      <c r="C5" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="3:6">
+      <c r="C6" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="23"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" spans="3:6">
+      <c r="C11" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="3:6">
+      <c r="C12" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="3:6">
+      <c r="C13" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="F13" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:F21"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="35.375" customWidth="1"/>
+    <col min="3" max="3" width="42.875" customWidth="1"/>
+    <col min="4" max="4" width="30.125" customWidth="1"/>
+    <col min="6" max="6" width="32.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4">
+      <c r="B3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="31"/>
+      <c r="B12" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="31"/>
+      <c r="B13" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="31"/>
+      <c r="B14" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="31"/>
+      <c r="C15" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="31"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="31"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="31"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="31"/>
+      <c r="B19" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="31"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="31"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:A21"/>
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
+++ b/internal_doc/05.测试设计/story/RocksDB/RocksDB测试设计.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="296">
   <si>
     <t>基本数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -519,10 +519,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，kill-9节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重复创建索引；索引字段相同；索引名相同</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -678,43 +674,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建索引过程中，正常重启备节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，异常重启主节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，异常重启备节点</t>
-  </si>
-  <si>
-    <t>创建索引过程中，正常重启主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，主节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，备节点磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>并发创建多个索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建索引过程中，主节点主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，备节点主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建索引过程中，全网掉电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>range范围切分，分区键为单个字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -809,10 +772,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存在单键索引、联合索引、非唯一索引、唯一索引、强制唯一索引，已存在数据，正常重启主节点、数据组所有节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（写缓存大小*个数）小于（实际物理内存+虚拟内存）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1209,6 +1168,42 @@
   </si>
   <si>
     <t>全网掉电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非唯一、唯一索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增删改查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建删除索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性（详见可靠性测试一页）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一个索引 不同索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据压缩 数据不压缩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1505,6 +1500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1517,7 +1513,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1880,7 +1875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2"/>
@@ -2012,7 +2007,7 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
@@ -2075,7 +2070,7 @@
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
@@ -2093,7 +2088,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" customHeight="1">
@@ -2107,7 +2102,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" customHeight="1">
@@ -2122,28 +2117,48 @@
     </row>
     <row r="40" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" customHeight="1">
       <c r="A44" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>157</v>
+    </row>
+    <row r="46" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A46" s="17" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A50" s="17" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +2179,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2175,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="72.375" style="11" customWidth="1"/>
@@ -2197,7 +2212,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2221,12 +2236,12 @@
         <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="5" customFormat="1">
@@ -2236,22 +2251,22 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="11" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
         <v>96</v>
@@ -2259,12 +2274,12 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -2290,17 +2305,17 @@
     </row>
     <row r="20" spans="1:2" s="19" customFormat="1">
       <c r="A20" s="18" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2315,7 +2330,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="11" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="5" customFormat="1">
@@ -2335,7 +2350,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="11" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2360,40 +2375,40 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="11" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:2" s="5" customFormat="1">
       <c r="A39" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="11" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="11" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2401,7 +2416,7 @@
         <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2409,7 +2424,7 @@
         <v>117</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2417,12 +2432,12 @@
         <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B47" s="15"/>
     </row>
@@ -2431,215 +2446,182 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="11" t="s">
-        <v>194</v>
+    <row r="49" spans="1:1">
+      <c r="A49" s="16"/>
+    </row>
+    <row r="50" spans="1:1" s="5" customFormat="1">
+      <c r="A50" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="11" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="11" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="11" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="11" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="11" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="11" t="s">
-        <v>169</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" s="5" customFormat="1">
+      <c r="A58" s="12" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="16"/>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="16"/>
-    </row>
-    <row r="63" spans="1:1" s="5" customFormat="1">
-      <c r="A63" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="11" t="s">
-        <v>127</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" s="5" customFormat="1">
+      <c r="A62" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" s="5" customFormat="1">
+      <c r="A65" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="11" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="11" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" s="5" customFormat="1">
-      <c r="A71" s="12" t="s">
-        <v>148</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="11" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:1" s="5" customFormat="1">
       <c r="A75" s="12" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="11" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:1" s="5" customFormat="1">
       <c r="A78" s="12" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="11" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="11" t="s">
-        <v>137</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" s="5" customFormat="1">
+      <c r="A82" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="11" t="s">
-        <v>149</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" s="5" customFormat="1">
+      <c r="A85" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="11" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:1" s="5" customFormat="1">
       <c r="A88" s="12" t="s">
-        <v>177</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" s="5" customFormat="1">
-      <c r="A91" s="12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" s="5" customFormat="1">
-      <c r="A95" s="12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" s="5" customFormat="1">
-      <c r="A98" s="12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="11" t="s">
-        <v>172</v>
+      <c r="A89" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A93" s="17" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -2781,7 +2763,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>73</v>
@@ -2807,7 +2789,7 @@
         <v>105</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>73</v>
@@ -2833,7 +2815,7 @@
         <v>90</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>111</v>
@@ -2859,7 +2841,7 @@
         <v>90</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>74</v>
@@ -2885,7 +2867,7 @@
         <v>105</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>74</v>
@@ -2911,7 +2893,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>111</v>
@@ -2937,7 +2919,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>111</v>
@@ -2955,7 +2937,7 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2977,246 +2959,246 @@
   <sheetData>
     <row r="5" spans="3:6">
       <c r="C5" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="3:6">
       <c r="C6" s="22" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="3:6">
       <c r="C7" s="24" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="24" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="24" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="3:6">
       <c r="C10" s="24" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="3:6">
       <c r="C11" s="24" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="3:6">
       <c r="C12" s="24" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="3:6">
       <c r="C13" s="24" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="3:6">
       <c r="C14" s="25" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="3:6">
       <c r="C15" s="22" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="3:6">
       <c r="C16" s="24" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="3:6">
       <c r="C17" s="24" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="3:6">
       <c r="C18" s="24" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="3:6">
       <c r="C19" s="25" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="3:6">
       <c r="C20" s="6" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="3:6">
       <c r="C21" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="3:6">
       <c r="C22" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="3:6">
       <c r="C23" s="22" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="3:6">
       <c r="C24" s="24" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="3:6">
       <c r="C25" s="25" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E25" s="26"/>
       <c r="F25" s="2"/>
@@ -3245,21 +3227,21 @@
   <sheetData>
     <row r="11" spans="2:4">
       <c r="B11" s="3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>72</v>
@@ -3267,10 +3249,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>72</v>
@@ -3278,10 +3260,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>72</v>
@@ -3289,10 +3271,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>72</v>
@@ -3300,10 +3282,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>72</v>
@@ -3311,10 +3293,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>72</v>
@@ -3322,35 +3304,35 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3372,119 +3354,119 @@
   <sheetData>
     <row r="2" spans="3:6">
       <c r="C2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="3:6">
       <c r="C3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="3:6">
       <c r="C5" s="22" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="F5" s="23"/>
     </row>
     <row r="6" spans="3:6">
       <c r="C6" s="22" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="3:6">
       <c r="C7" s="24" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="F8" s="11"/>
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>270</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="3:6">
       <c r="C10" s="22" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="3:6">
       <c r="C11" s="24" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="3:6">
       <c r="C12" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F12" s="11"/>
     </row>
     <row r="13" spans="3:6">
       <c r="C13" s="25" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F13" s="26"/>
     </row>
@@ -3497,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:F21"/>
+  <dimension ref="A9:F25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="35.375" customWidth="1"/>
@@ -3506,165 +3488,165 @@
     <col min="6" max="6" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4">
-      <c r="B3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="B4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" t="s">
-        <v>278</v>
-      </c>
-    </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="34"/>
+      <c r="A9" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="35"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="30" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="31" t="s">
-        <v>294</v>
+      <c r="A11" s="32" t="s">
+        <v>283</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="31"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="6" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>280</v>
+        <v>269</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="31"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="31"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="6" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="31"/>
+      <c r="A15" s="32"/>
       <c r="C15" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>283</v>
+        <v>272</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="31"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>284</v>
+        <v>273</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="31"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="F17" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>296</v>
-      </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="31"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="32"/>
+      <c r="B19" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="31"/>
-      <c r="B19" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>287</v>
+      <c r="D19" s="31" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="31"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="31"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>289</v>
+        <v>278</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="C23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="C24" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="C25" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
